--- a/NuevaData/Presentacion/Profundizacion/FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO/d. Construcción de reportes/F11_Autoevaluacion_2025_vs_2026_Profundizacion.xlsx
+++ b/NuevaData/Presentacion/Profundizacion/FACTOR 11. ORGANIZACIÓN, ADMINISTRACIÓN Y FINANCIACIÓN DEL PROGRAMA ACADÉMICO/d. Construcción de reportes/F11_Autoevaluacion_2025_vs_2026_Profundizacion.xlsx
@@ -667,18 +667,14 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A10" s="9" t="n">
+        <v>53</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E10" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>9</v>
@@ -697,10 +693,8 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A13" s="9" t="n">
+        <v>36</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>2</v>
